--- a/excel/1000(n)/Sort_Dataset.xlsx
+++ b/excel/1000(n)/Sort_Dataset.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="28">
   <si>
     <t xml:space="preserve">Algorithm </t>
   </si>
@@ -222,67 +222,67 @@
         <v>1000.0</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>424600.0</v>
+        <v>297300.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>94500.0</v>
+        <v>305400.0</v>
       </c>
       <c r="E2" t="n" s="0">
-        <v>334900.0</v>
+        <v>94900.0</v>
       </c>
       <c r="F2" t="n" s="0">
-        <v>308500.0</v>
+        <v>193000.0</v>
       </c>
       <c r="G2" t="n" s="0">
-        <v>320400.0</v>
+        <v>94600.0</v>
       </c>
       <c r="H2" t="n" s="0">
-        <v>110000.0</v>
+        <v>95300.0</v>
       </c>
       <c r="I2" t="n" s="0">
-        <v>166500.0</v>
+        <v>160000.0</v>
       </c>
       <c r="J2" t="n" s="0">
-        <v>96000.0</v>
+        <v>94300.0</v>
       </c>
       <c r="K2" t="n" s="0">
-        <v>303800.0</v>
+        <v>94900.0</v>
       </c>
       <c r="L2" t="n" s="0">
-        <v>94400.0</v>
+        <v>94700.0</v>
       </c>
       <c r="M2" t="n" s="0">
-        <v>99200.0</v>
+        <v>193600.0</v>
       </c>
       <c r="N2" t="n" s="0">
-        <v>97700.0</v>
+        <v>95300.0</v>
       </c>
       <c r="O2" t="n" s="0">
-        <v>320300.0</v>
+        <v>95000.0</v>
       </c>
       <c r="P2" t="n" s="0">
-        <v>97600.0</v>
+        <v>299100.0</v>
       </c>
       <c r="Q2" t="n" s="0">
-        <v>104800.0</v>
+        <v>213800.0</v>
       </c>
       <c r="R2" t="n" s="0">
-        <v>109200.0</v>
+        <v>98100.0</v>
       </c>
       <c r="S2" t="n" s="0">
-        <v>96000.0</v>
+        <v>95400.0</v>
       </c>
       <c r="T2" t="n" s="0">
-        <v>104600.0</v>
+        <v>325700.0</v>
       </c>
       <c r="U2" t="n" s="0">
         <v>99900.0</v>
       </c>
       <c r="V2" t="n" s="0">
-        <v>263000.0</v>
+        <v>191700.0</v>
       </c>
       <c r="W2" t="n" s="0">
-        <v>182295.0</v>
+        <v>161600.0</v>
       </c>
     </row>
     <row r="3">
@@ -293,28 +293,28 @@
         <v>1000.0</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>3800.0</v>
+        <v>2300.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>6000.0</v>
+        <v>1700.0</v>
       </c>
       <c r="E3" t="n" s="0">
-        <v>12600.0</v>
+        <v>1700.0</v>
       </c>
       <c r="F3" t="n" s="0">
-        <v>2700.0</v>
+        <v>1000.0</v>
       </c>
       <c r="G3" t="n" s="0">
-        <v>1200.0</v>
+        <v>1300.0</v>
       </c>
       <c r="H3" t="n" s="0">
-        <v>1700.0</v>
+        <v>900.0</v>
       </c>
       <c r="I3" t="n" s="0">
-        <v>2400.0</v>
+        <v>1500.0</v>
       </c>
       <c r="J3" t="n" s="0">
-        <v>1000.0</v>
+        <v>1300.0</v>
       </c>
       <c r="K3" t="n" s="0">
         <v>900.0</v>
@@ -323,37 +323,37 @@
         <v>800.0</v>
       </c>
       <c r="M3" t="n" s="0">
-        <v>900.0</v>
+        <v>1000.0</v>
       </c>
       <c r="N3" t="n" s="0">
-        <v>800.0</v>
+        <v>2500.0</v>
       </c>
       <c r="O3" t="n" s="0">
         <v>800.0</v>
       </c>
       <c r="P3" t="n" s="0">
-        <v>1600.0</v>
+        <v>800.0</v>
       </c>
       <c r="Q3" t="n" s="0">
         <v>800.0</v>
       </c>
       <c r="R3" t="n" s="0">
-        <v>800.0</v>
+        <v>1700.0</v>
       </c>
       <c r="S3" t="n" s="0">
         <v>800.0</v>
       </c>
       <c r="T3" t="n" s="0">
-        <v>1500.0</v>
+        <v>800.0</v>
       </c>
       <c r="U3" t="n" s="0">
+        <v>900.0</v>
+      </c>
+      <c r="V3" t="n" s="0">
         <v>700.0</v>
       </c>
-      <c r="V3" t="n" s="0">
-        <v>800.0</v>
-      </c>
       <c r="W3" t="n" s="0">
-        <v>2130.0</v>
+        <v>1210.0</v>
       </c>
     </row>
     <row r="4">
@@ -364,67 +364,67 @@
         <v>1000.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>738900.0</v>
+        <v>408100.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>174200.0</v>
+        <v>182200.0</v>
       </c>
       <c r="E4" t="n" s="0">
+        <v>179100.0</v>
+      </c>
+      <c r="F4" t="n" s="0">
         <v>175100.0</v>
       </c>
-      <c r="F4" t="n" s="0">
-        <v>281400.0</v>
-      </c>
       <c r="G4" t="n" s="0">
-        <v>262000.0</v>
+        <v>270700.0</v>
       </c>
       <c r="H4" t="n" s="0">
-        <v>274700.0</v>
+        <v>237200.0</v>
       </c>
       <c r="I4" t="n" s="0">
-        <v>415500.0</v>
+        <v>182400.0</v>
       </c>
       <c r="J4" t="n" s="0">
-        <v>176200.0</v>
+        <v>172600.0</v>
       </c>
       <c r="K4" t="n" s="0">
-        <v>320500.0</v>
+        <v>172800.0</v>
       </c>
       <c r="L4" t="n" s="0">
-        <v>251300.0</v>
+        <v>173600.0</v>
       </c>
       <c r="M4" t="n" s="0">
-        <v>173100.0</v>
+        <v>174300.0</v>
       </c>
       <c r="N4" t="n" s="0">
-        <v>173700.0</v>
+        <v>201100.0</v>
       </c>
       <c r="O4" t="n" s="0">
-        <v>176900.0</v>
+        <v>172700.0</v>
       </c>
       <c r="P4" t="n" s="0">
-        <v>173500.0</v>
+        <v>172800.0</v>
       </c>
       <c r="Q4" t="n" s="0">
-        <v>177200.0</v>
+        <v>172700.0</v>
       </c>
       <c r="R4" t="n" s="0">
-        <v>176000.0</v>
+        <v>419800.0</v>
       </c>
       <c r="S4" t="n" s="0">
-        <v>174000.0</v>
+        <v>173300.0</v>
       </c>
       <c r="T4" t="n" s="0">
-        <v>173400.0</v>
+        <v>172900.0</v>
       </c>
       <c r="U4" t="n" s="0">
-        <v>198700.0</v>
+        <v>179700.0</v>
       </c>
       <c r="V4" t="n" s="0">
-        <v>172700.0</v>
+        <v>444600.0</v>
       </c>
       <c r="W4" t="n" s="0">
-        <v>241950.0</v>
+        <v>221885.0</v>
       </c>
     </row>
     <row r="5">
@@ -435,67 +435,67 @@
         <v>1000.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>69600.0</v>
+        <v>85500.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>41800.0</v>
+        <v>59200.0</v>
       </c>
       <c r="E5" t="n" s="0">
-        <v>67600.0</v>
+        <v>36700.0</v>
       </c>
       <c r="F5" t="n" s="0">
-        <v>33900.0</v>
+        <v>24900.0</v>
       </c>
       <c r="G5" t="n" s="0">
-        <v>34300.0</v>
+        <v>31100.0</v>
       </c>
       <c r="H5" t="n" s="0">
-        <v>51200.0</v>
+        <v>51900.0</v>
       </c>
       <c r="I5" t="n" s="0">
-        <v>47600.0</v>
+        <v>5381800.0</v>
       </c>
       <c r="J5" t="n" s="0">
-        <v>30000.0</v>
+        <v>38800.0</v>
       </c>
       <c r="K5" t="n" s="0">
+        <v>30900.0</v>
+      </c>
+      <c r="L5" t="n" s="0">
+        <v>42600.0</v>
+      </c>
+      <c r="M5" t="n" s="0">
         <v>26200.0</v>
       </c>
-      <c r="L5" t="n" s="0">
-        <v>46800.0</v>
-      </c>
-      <c r="M5" t="n" s="0">
-        <v>40400.0</v>
-      </c>
       <c r="N5" t="n" s="0">
-        <v>27000.0</v>
+        <v>41500.0</v>
       </c>
       <c r="O5" t="n" s="0">
-        <v>47500.0</v>
+        <v>25100.0</v>
       </c>
       <c r="P5" t="n" s="0">
-        <v>25800.0</v>
+        <v>64300.0</v>
       </c>
       <c r="Q5" t="n" s="0">
-        <v>32400.0</v>
+        <v>33300.0</v>
       </c>
       <c r="R5" t="n" s="0">
-        <v>41900.0</v>
+        <v>33800.0</v>
       </c>
       <c r="S5" t="n" s="0">
-        <v>26300.0</v>
+        <v>27500.0</v>
       </c>
       <c r="T5" t="n" s="0">
-        <v>26300.0</v>
+        <v>43100.0</v>
       </c>
       <c r="U5" t="n" s="0">
-        <v>32700.0</v>
+        <v>37800.0</v>
       </c>
       <c r="V5" t="n" s="0">
-        <v>29500.0</v>
+        <v>54100.0</v>
       </c>
       <c r="W5" t="n" s="0">
-        <v>38940.0</v>
+        <v>308505.0</v>
       </c>
     </row>
     <row r="6">
@@ -506,67 +506,67 @@
         <v>1000.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>68600.0</v>
+        <v>57500.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>54500.0</v>
+        <v>100000.0</v>
       </c>
       <c r="E6" t="n" s="0">
-        <v>70500.0</v>
+        <v>99800.0</v>
       </c>
       <c r="F6" t="n" s="0">
-        <v>54800.0</v>
+        <v>51400.0</v>
       </c>
       <c r="G6" t="n" s="0">
-        <v>52200.0</v>
+        <v>97100.0</v>
       </c>
       <c r="H6" t="n" s="0">
-        <v>61500.0</v>
+        <v>85400.0</v>
       </c>
       <c r="I6" t="n" s="0">
-        <v>87700.0</v>
+        <v>57800.0</v>
       </c>
       <c r="J6" t="n" s="0">
-        <v>84300.0</v>
+        <v>79600.0</v>
       </c>
       <c r="K6" t="n" s="0">
-        <v>51900.0</v>
+        <v>43800.0</v>
       </c>
       <c r="L6" t="n" s="0">
-        <v>64100.0</v>
+        <v>45000.0</v>
       </c>
       <c r="M6" t="n" s="0">
-        <v>46600.0</v>
+        <v>69600.0</v>
       </c>
       <c r="N6" t="n" s="0">
-        <v>41700.0</v>
+        <v>61700.0</v>
       </c>
       <c r="O6" t="n" s="0">
-        <v>49700.0</v>
+        <v>46900.0</v>
       </c>
       <c r="P6" t="n" s="0">
-        <v>40300.0</v>
+        <v>85700.0</v>
       </c>
       <c r="Q6" t="n" s="0">
-        <v>69800.0</v>
+        <v>47400.0</v>
       </c>
       <c r="R6" t="n" s="0">
-        <v>53500.0</v>
+        <v>42100.0</v>
       </c>
       <c r="S6" t="n" s="0">
-        <v>47500.0</v>
+        <v>49000.0</v>
       </c>
       <c r="T6" t="n" s="0">
-        <v>40100.0</v>
+        <v>100100.0</v>
       </c>
       <c r="U6" t="n" s="0">
-        <v>45700.0</v>
+        <v>51400.0</v>
       </c>
       <c r="V6" t="n" s="0">
-        <v>55000.0</v>
+        <v>92100.0</v>
       </c>
       <c r="W6" t="n" s="0">
-        <v>57000.0</v>
+        <v>68170.0</v>
       </c>
     </row>
   </sheetData>

--- a/excel/1000(n)/Sort_Dataset.xlsx
+++ b/excel/1000(n)/Sort_Dataset.xlsx
@@ -222,67 +222,67 @@
         <v>1000.0</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>297300.0</v>
+        <v>106500.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>305400.0</v>
+        <v>328000.0</v>
       </c>
       <c r="E2" t="n" s="0">
-        <v>94900.0</v>
+        <v>303000.0</v>
       </c>
       <c r="F2" t="n" s="0">
-        <v>193000.0</v>
+        <v>314000.0</v>
       </c>
       <c r="G2" t="n" s="0">
+        <v>317700.0</v>
+      </c>
+      <c r="H2" t="n" s="0">
+        <v>115000.0</v>
+      </c>
+      <c r="I2" t="n" s="0">
+        <v>311200.0</v>
+      </c>
+      <c r="J2" t="n" s="0">
+        <v>99300.0</v>
+      </c>
+      <c r="K2" t="n" s="0">
+        <v>211200.0</v>
+      </c>
+      <c r="L2" t="n" s="0">
+        <v>97300.0</v>
+      </c>
+      <c r="M2" t="n" s="0">
+        <v>141400.0</v>
+      </c>
+      <c r="N2" t="n" s="0">
         <v>94600.0</v>
       </c>
-      <c r="H2" t="n" s="0">
-        <v>95300.0</v>
-      </c>
-      <c r="I2" t="n" s="0">
-        <v>160000.0</v>
-      </c>
-      <c r="J2" t="n" s="0">
-        <v>94300.0</v>
-      </c>
-      <c r="K2" t="n" s="0">
-        <v>94900.0</v>
-      </c>
-      <c r="L2" t="n" s="0">
-        <v>94700.0</v>
-      </c>
-      <c r="M2" t="n" s="0">
-        <v>193600.0</v>
-      </c>
-      <c r="N2" t="n" s="0">
-        <v>95300.0</v>
-      </c>
       <c r="O2" t="n" s="0">
-        <v>95000.0</v>
+        <v>113900.0</v>
       </c>
       <c r="P2" t="n" s="0">
-        <v>299100.0</v>
+        <v>94600.0</v>
       </c>
       <c r="Q2" t="n" s="0">
-        <v>213800.0</v>
+        <v>96300.0</v>
       </c>
       <c r="R2" t="n" s="0">
-        <v>98100.0</v>
+        <v>95400.0</v>
       </c>
       <c r="S2" t="n" s="0">
-        <v>95400.0</v>
+        <v>94100.0</v>
       </c>
       <c r="T2" t="n" s="0">
-        <v>325700.0</v>
+        <v>100800.0</v>
       </c>
       <c r="U2" t="n" s="0">
-        <v>99900.0</v>
+        <v>192900.0</v>
       </c>
       <c r="V2" t="n" s="0">
-        <v>191700.0</v>
+        <v>299600.0</v>
       </c>
       <c r="W2" t="n" s="0">
-        <v>161600.0</v>
+        <v>176340.0</v>
       </c>
     </row>
     <row r="3">
@@ -293,67 +293,67 @@
         <v>1000.0</v>
       </c>
       <c r="C3" t="n" s="0">
+        <v>2700.0</v>
+      </c>
+      <c r="D3" t="n" s="0">
+        <v>2400.0</v>
+      </c>
+      <c r="E3" t="n" s="0">
         <v>2300.0</v>
       </c>
-      <c r="D3" t="n" s="0">
+      <c r="F3" t="n" s="0">
+        <v>1600.0</v>
+      </c>
+      <c r="G3" t="n" s="0">
+        <v>4200.0</v>
+      </c>
+      <c r="H3" t="n" s="0">
         <v>1700.0</v>
       </c>
-      <c r="E3" t="n" s="0">
-        <v>1700.0</v>
-      </c>
-      <c r="F3" t="n" s="0">
-        <v>1000.0</v>
-      </c>
-      <c r="G3" t="n" s="0">
-        <v>1300.0</v>
-      </c>
-      <c r="H3" t="n" s="0">
+      <c r="I3" t="n" s="0">
+        <v>1400.0</v>
+      </c>
+      <c r="J3" t="n" s="0">
         <v>900.0</v>
       </c>
-      <c r="I3" t="n" s="0">
-        <v>1500.0</v>
-      </c>
-      <c r="J3" t="n" s="0">
-        <v>1300.0</v>
-      </c>
       <c r="K3" t="n" s="0">
+        <v>2100.0</v>
+      </c>
+      <c r="L3" t="n" s="0">
         <v>900.0</v>
       </c>
-      <c r="L3" t="n" s="0">
+      <c r="M3" t="n" s="0">
         <v>800.0</v>
       </c>
-      <c r="M3" t="n" s="0">
-        <v>1000.0</v>
-      </c>
       <c r="N3" t="n" s="0">
-        <v>2500.0</v>
+        <v>900.0</v>
       </c>
       <c r="O3" t="n" s="0">
         <v>800.0</v>
       </c>
       <c r="P3" t="n" s="0">
-        <v>800.0</v>
+        <v>900.0</v>
       </c>
       <c r="Q3" t="n" s="0">
-        <v>800.0</v>
+        <v>700.0</v>
       </c>
       <c r="R3" t="n" s="0">
-        <v>1700.0</v>
+        <v>1400.0</v>
       </c>
       <c r="S3" t="n" s="0">
         <v>800.0</v>
       </c>
       <c r="T3" t="n" s="0">
-        <v>800.0</v>
+        <v>1400.0</v>
       </c>
       <c r="U3" t="n" s="0">
-        <v>900.0</v>
+        <v>700.0</v>
       </c>
       <c r="V3" t="n" s="0">
-        <v>700.0</v>
+        <v>1500.0</v>
       </c>
       <c r="W3" t="n" s="0">
-        <v>1210.0</v>
+        <v>1505.0</v>
       </c>
     </row>
     <row r="4">
@@ -364,67 +364,67 @@
         <v>1000.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>408100.0</v>
+        <v>276700.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>182200.0</v>
+        <v>410000.0</v>
       </c>
       <c r="E4" t="n" s="0">
-        <v>179100.0</v>
+        <v>440700.0</v>
       </c>
       <c r="F4" t="n" s="0">
-        <v>175100.0</v>
+        <v>414200.0</v>
       </c>
       <c r="G4" t="n" s="0">
-        <v>270700.0</v>
+        <v>174600.0</v>
       </c>
       <c r="H4" t="n" s="0">
-        <v>237200.0</v>
+        <v>411200.0</v>
       </c>
       <c r="I4" t="n" s="0">
-        <v>182400.0</v>
+        <v>313800.0</v>
       </c>
       <c r="J4" t="n" s="0">
-        <v>172600.0</v>
+        <v>187000.0</v>
       </c>
       <c r="K4" t="n" s="0">
-        <v>172800.0</v>
+        <v>286800.0</v>
       </c>
       <c r="L4" t="n" s="0">
-        <v>173600.0</v>
+        <v>177400.0</v>
       </c>
       <c r="M4" t="n" s="0">
-        <v>174300.0</v>
+        <v>173800.0</v>
       </c>
       <c r="N4" t="n" s="0">
-        <v>201100.0</v>
+        <v>173300.0</v>
       </c>
       <c r="O4" t="n" s="0">
-        <v>172700.0</v>
+        <v>172900.0</v>
       </c>
       <c r="P4" t="n" s="0">
-        <v>172800.0</v>
+        <v>178100.0</v>
       </c>
       <c r="Q4" t="n" s="0">
         <v>172700.0</v>
       </c>
       <c r="R4" t="n" s="0">
-        <v>419800.0</v>
+        <v>173000.0</v>
       </c>
       <c r="S4" t="n" s="0">
-        <v>173300.0</v>
+        <v>172800.0</v>
       </c>
       <c r="T4" t="n" s="0">
+        <v>415900.0</v>
+      </c>
+      <c r="U4" t="n" s="0">
         <v>172900.0</v>
       </c>
-      <c r="U4" t="n" s="0">
-        <v>179700.0</v>
-      </c>
       <c r="V4" t="n" s="0">
-        <v>444600.0</v>
+        <v>418200.0</v>
       </c>
       <c r="W4" t="n" s="0">
-        <v>221885.0</v>
+        <v>265800.0</v>
       </c>
     </row>
     <row r="5">
@@ -435,67 +435,67 @@
         <v>1000.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>85500.0</v>
+        <v>67200.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>59200.0</v>
+        <v>77800.0</v>
       </c>
       <c r="E5" t="n" s="0">
-        <v>36700.0</v>
+        <v>66000.0</v>
       </c>
       <c r="F5" t="n" s="0">
-        <v>24900.0</v>
+        <v>51800.0</v>
       </c>
       <c r="G5" t="n" s="0">
-        <v>31100.0</v>
+        <v>25600.0</v>
       </c>
       <c r="H5" t="n" s="0">
-        <v>51900.0</v>
+        <v>54800.0</v>
       </c>
       <c r="I5" t="n" s="0">
-        <v>5381800.0</v>
+        <v>62700.0</v>
       </c>
       <c r="J5" t="n" s="0">
-        <v>38800.0</v>
+        <v>27200.0</v>
       </c>
       <c r="K5" t="n" s="0">
-        <v>30900.0</v>
+        <v>30700.0</v>
       </c>
       <c r="L5" t="n" s="0">
-        <v>42600.0</v>
+        <v>34400.0</v>
       </c>
       <c r="M5" t="n" s="0">
+        <v>39500.0</v>
+      </c>
+      <c r="N5" t="n" s="0">
+        <v>52500.0</v>
+      </c>
+      <c r="O5" t="n" s="0">
+        <v>23900.0</v>
+      </c>
+      <c r="P5" t="n" s="0">
+        <v>31500.0</v>
+      </c>
+      <c r="Q5" t="n" s="0">
+        <v>32000.0</v>
+      </c>
+      <c r="R5" t="n" s="0">
+        <v>26500.0</v>
+      </c>
+      <c r="S5" t="n" s="0">
+        <v>26000.0</v>
+      </c>
+      <c r="T5" t="n" s="0">
         <v>26200.0</v>
       </c>
-      <c r="N5" t="n" s="0">
-        <v>41500.0</v>
-      </c>
-      <c r="O5" t="n" s="0">
-        <v>25100.0</v>
-      </c>
-      <c r="P5" t="n" s="0">
-        <v>64300.0</v>
-      </c>
-      <c r="Q5" t="n" s="0">
-        <v>33300.0</v>
-      </c>
-      <c r="R5" t="n" s="0">
-        <v>33800.0</v>
-      </c>
-      <c r="S5" t="n" s="0">
-        <v>27500.0</v>
-      </c>
-      <c r="T5" t="n" s="0">
-        <v>43100.0</v>
-      </c>
       <c r="U5" t="n" s="0">
-        <v>37800.0</v>
+        <v>28700.0</v>
       </c>
       <c r="V5" t="n" s="0">
-        <v>54100.0</v>
+        <v>56400.0</v>
       </c>
       <c r="W5" t="n" s="0">
-        <v>308505.0</v>
+        <v>42070.0</v>
       </c>
     </row>
     <row r="6">
@@ -506,67 +506,67 @@
         <v>1000.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>57500.0</v>
+        <v>97600.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>100000.0</v>
+        <v>97300.0</v>
       </c>
       <c r="E6" t="n" s="0">
-        <v>99800.0</v>
+        <v>99600.0</v>
       </c>
       <c r="F6" t="n" s="0">
-        <v>51400.0</v>
+        <v>66100.0</v>
       </c>
       <c r="G6" t="n" s="0">
-        <v>97100.0</v>
+        <v>91300.0</v>
       </c>
       <c r="H6" t="n" s="0">
-        <v>85400.0</v>
+        <v>67600.0</v>
       </c>
       <c r="I6" t="n" s="0">
-        <v>57800.0</v>
+        <v>86000.0</v>
       </c>
       <c r="J6" t="n" s="0">
-        <v>79600.0</v>
+        <v>54100.0</v>
       </c>
       <c r="K6" t="n" s="0">
-        <v>43800.0</v>
+        <v>51100.0</v>
       </c>
       <c r="L6" t="n" s="0">
-        <v>45000.0</v>
+        <v>49100.0</v>
       </c>
       <c r="M6" t="n" s="0">
-        <v>69600.0</v>
+        <v>77200.0</v>
       </c>
       <c r="N6" t="n" s="0">
-        <v>61700.0</v>
+        <v>71300.0</v>
       </c>
       <c r="O6" t="n" s="0">
-        <v>46900.0</v>
+        <v>55500.0</v>
       </c>
       <c r="P6" t="n" s="0">
-        <v>85700.0</v>
+        <v>47700.0</v>
       </c>
       <c r="Q6" t="n" s="0">
-        <v>47400.0</v>
+        <v>53800.0</v>
       </c>
       <c r="R6" t="n" s="0">
-        <v>42100.0</v>
+        <v>47000.0</v>
       </c>
       <c r="S6" t="n" s="0">
-        <v>49000.0</v>
+        <v>48800.0</v>
       </c>
       <c r="T6" t="n" s="0">
-        <v>100100.0</v>
+        <v>48600.0</v>
       </c>
       <c r="U6" t="n" s="0">
-        <v>51400.0</v>
+        <v>50300.0</v>
       </c>
       <c r="V6" t="n" s="0">
-        <v>92100.0</v>
+        <v>86800.0</v>
       </c>
       <c r="W6" t="n" s="0">
-        <v>68170.0</v>
+        <v>67340.0</v>
       </c>
     </row>
   </sheetData>
